--- a/InputData/add-outputs/VoaSL/Value of a Statistical Life.xlsx
+++ b/InputData/add-outputs/VoaSL/Value of a Statistical Life.xlsx
@@ -1,24 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10111"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28318"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anaxolt/Google Drive/2021/D.Development/20210316_3.2 schema/eps-mex2021-pre_build_20210316/InputData/add-outputs/VoaSL/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreazafra/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AE9CCC39-2AD7-E04C-9B6E-1F3869E53B8D}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{6E7A770A-7C28-0545-8D7C-1EB6139DDDB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C07C382-D83B-4BDF-89DC-90D091D010E7}"/>
   <bookViews>
-    <workbookView xWindow="880" yWindow="500" windowWidth="14240" windowHeight="18740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="35080" yWindow="2640" windowWidth="27000" windowHeight="18160" firstSheet="2" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="Mexico" sheetId="4" r:id="rId2"/>
     <sheet name="VoaSL" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -26,6 +29,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -33,117 +38,116 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
   <si>
     <t>VoaSL Value of a Statistical Life</t>
   </si>
   <si>
+    <t>Mexico:</t>
+  </si>
+  <si>
+    <t>Becerra-Pérez, L. A., Ramos-Alvarez, R. A., DelaCruz, J. J., &amp; García-Páez, B. (2024). Value per Statistical Life at the Sub-National Level as a Tool for Assessing Public Health and Environmental Problems. INQUIRY: The Journal of Health Care Organization, Provision, and Financing, 61, 00469580241246476.</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/38641976/</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>This variable is used to convert from dollars (in the SCoHIbP Social Cost of</t>
+  </si>
+  <si>
+    <t>Health Impacts by Pollutant variable) into human lives, so the VSL figure</t>
+  </si>
+  <si>
+    <t>here must reflect the one used to calculate the health impacts in that</t>
+  </si>
+  <si>
+    <t>variable for the result to be accurate.</t>
+  </si>
+  <si>
+    <t>Currency Year Adjustment</t>
+  </si>
+  <si>
+    <t>We adjust 2014 dollars to 2012 dollars using the following conversion factor:</t>
+  </si>
+  <si>
+    <t>We adjust 2021 dollars to 2012 dollars using the following conversion factor:</t>
+  </si>
+  <si>
     <t>See "cpi.xlsx" in the InputData folder for source information.</t>
   </si>
   <si>
-    <t>Notes</t>
+    <t>Currency conversions</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>MXN/USD</t>
+  </si>
+  <si>
+    <t>Central Mexico Megalopolis - Air quality program numbers</t>
+  </si>
+  <si>
+    <t>https://framework-gb.cdn.gob.mx/data/institutos/semarnat/Programa_de_Gesti%C3%B3n_Federal_2017-2030_final.pdf</t>
+  </si>
+  <si>
+    <t>https://www.gob.mx/cms/uploads/attachment/file/436696/Informe_final_VEV_vf.pdf</t>
+  </si>
+  <si>
+    <t>Value per Statistical Life at the Sub-National Level as a Tool for Assessing Public Health and Environmental Problems</t>
+  </si>
+  <si>
+    <t>Value of a statistical Life (VSL)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This article aims to estimate the Value per Statistical Life (VSL) and Value per Statistical Life Year (VSLY) at the sub-national level, which can be used to calculate the economic impact of health and environmental problems. We estimate the value of life for Mexico and its 32 states, grouped into 5 regions for 2021. We used the OECD's guidelines on "Mortality Risk Valuation in Environment, Health and Transport Policies," which applies the measure of Willingness to Pay (WTP) and Cost-Benefit Analysis (CBA). Mexico's overall VSL of $2 000 000 USD in 2021 showcases the value placed on human life (3). </t>
+  </si>
+  <si>
+    <t>MXN, 2014</t>
+  </si>
+  <si>
+    <t>USD, 2014</t>
+  </si>
+  <si>
+    <t>USD, 2012</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>VSL1 - Local contingency valuation study</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VSL2- Local contingency valuation study </t>
+  </si>
+  <si>
+    <t>VSL2 - International estimate, adjusted to Mexico</t>
+  </si>
+  <si>
+    <t>USD, 2021</t>
+  </si>
+  <si>
+    <t>VSL3 - OECD guidelines - Mexico case</t>
   </si>
   <si>
     <t>Statistical Life</t>
   </si>
   <si>
     <t>Value (2012$)</t>
-  </si>
-  <si>
-    <t>This variable is used to convert from dollars (in the SCoHIbP Social Cost of</t>
-  </si>
-  <si>
-    <t>Health Impacts by Pollutant variable) into human lives, so the VSL figure</t>
-  </si>
-  <si>
-    <t>here must reflect the one used to calculate the health impacts in that</t>
-  </si>
-  <si>
-    <t>variable for the result to be accurate.</t>
-  </si>
-  <si>
-    <t>Currency Year Adjustment</t>
-  </si>
-  <si>
-    <t>Mexico:</t>
-  </si>
-  <si>
-    <t>INECC - Instituto Nacional de Ecología y Cambio Climático</t>
-  </si>
-  <si>
-    <t>PROAIRE - Megalópolis 2017-2030</t>
-  </si>
-  <si>
-    <t>https://framework-gb.cdn.gob.mx/data/institutos/semarnat/Programa_de_Gesti%C3%B3n_Federal_2017-2030_final.pdf</t>
-  </si>
-  <si>
-    <t>III. IMPACTOS DE LA CONTAMINACIÓN ATMOSFÉRICA, pg.96</t>
-  </si>
-  <si>
-    <t>Central Mexico Megalopolis - Air quality program numbers</t>
-  </si>
-  <si>
-    <t>Value of a statistical Life (VSL)</t>
-  </si>
-  <si>
-    <t>Valores de una Vida Estadística “VVE” seleccionados para el estudio: 1.6 millones de pesos y 13.85 millones de pesos (MXN, 2014), respectivamente. El primero corresponde a un VVE local que resulta del estudio de valoración contingente más reciente que se haya realizado en México, en tanto que el segundo corresponde a un VVE estimado internacionalmente ajustado por ingreso para México y que ha sido usado con anterioridad en diversos análisis de este tipo en el país (INECC, 2016c).</t>
-  </si>
-  <si>
-    <t>MXN, 2014</t>
-  </si>
-  <si>
-    <t>USD, 2012</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>VSL1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> - Local contingency valuation study</t>
-    </r>
-  </si>
-  <si>
-    <t>VSL2 - International estimate, adjusted to Mexico</t>
-  </si>
-  <si>
-    <t>USD, 2014</t>
-  </si>
-  <si>
-    <t>Year</t>
-  </si>
-  <si>
-    <t>MXN/USD</t>
-  </si>
-  <si>
-    <t>We adjust 2014 dollars to 2012 dollars using the following conversion factor:</t>
-  </si>
-  <si>
-    <t>Currency conversions</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -207,11 +211,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -235,9 +239,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -275,9 +279,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -310,26 +314,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -362,26 +349,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -555,306 +525,394 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:B37"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="38.33203125" customWidth="1"/>
+    <col min="2" max="2" width="38.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="B4" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="1"/>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>0.97135205460935392</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B4" s="2">
+    <row r="16" spans="1:2">
+      <c r="A16">
+        <v>0.84730412960844359</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21">
+        <v>2006</v>
+      </c>
+      <c r="B21">
+        <v>10.901017260273969</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
+        <v>2007</v>
+      </c>
+      <c r="B22">
+        <v>10.926903013698627</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>2008</v>
+      </c>
+      <c r="B23">
+        <v>11.138301912568313</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24">
+        <v>2009</v>
+      </c>
+      <c r="B24">
+        <v>13.509501369863028</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25">
+        <v>2010</v>
+      </c>
+      <c r="B25">
+        <v>12.636678082191793</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26">
+        <v>2011</v>
+      </c>
+      <c r="B26">
+        <v>12.427292876712329</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27">
+        <v>2012</v>
+      </c>
+      <c r="B27">
+        <v>13.168531967213106</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28">
+        <v>2013</v>
+      </c>
+      <c r="B28">
+        <v>12.767464383561641</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29">
+        <v>2014</v>
+      </c>
+      <c r="B29">
+        <v>13.298290410958895</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30">
+        <v>2015</v>
+      </c>
+      <c r="B30">
+        <v>15.854175890410984</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31">
+        <v>2016</v>
+      </c>
+      <c r="B31">
+        <v>18.656701092896164</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32">
         <v>2017</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B5" t="s">
+      <c r="B32">
+        <v>18.929111232876703</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33">
+        <v>2018</v>
+      </c>
+      <c r="B33">
+        <v>18.822825165562914</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34">
+        <v>2019</v>
+      </c>
+      <c r="B34">
+        <v>19.260525900000001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35">
+        <v>2020</v>
+      </c>
+      <c r="B35">
+        <v>21.493461509999999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36">
+        <v>2021</v>
+      </c>
+      <c r="B36">
+        <v>20.280012648221323</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B6" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" s="1"/>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>0.97135205460935392</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>23</v>
-      </c>
-      <c r="B21" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22">
-        <v>2006</v>
-      </c>
-      <c r="B22">
-        <v>10.901017260273969</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23">
-        <v>2007</v>
-      </c>
-      <c r="B23">
-        <v>10.926903013698627</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24">
-        <v>2008</v>
-      </c>
-      <c r="B24">
-        <v>11.138301912568313</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25">
-        <v>2009</v>
-      </c>
-      <c r="B25">
-        <v>13.509501369863028</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26">
-        <v>2010</v>
-      </c>
-      <c r="B26">
-        <v>12.636678082191793</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27">
-        <v>2011</v>
-      </c>
-      <c r="B27">
-        <v>12.427292876712329</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A28">
-        <v>2012</v>
-      </c>
-      <c r="B28">
-        <v>13.168531967213106</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A29">
-        <v>2013</v>
-      </c>
-      <c r="B29">
-        <v>12.767464383561641</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A30">
-        <v>2014</v>
-      </c>
-      <c r="B30">
-        <v>13.298290410958895</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A31">
-        <v>2015</v>
-      </c>
-      <c r="B31">
-        <v>15.854175890410984</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A32">
-        <v>2016</v>
-      </c>
-      <c r="B32">
-        <v>18.656701092896164</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A33">
-        <v>2017</v>
-      </c>
-      <c r="B33">
-        <v>18.929111232876703</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A34">
-        <v>2018</v>
-      </c>
-      <c r="B34">
-        <v>18.822825165562914</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B6" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="43.33203125" customWidth="1"/>
-    <col min="5" max="5" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.28515625" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>1</v>
+      </c>
       <c r="B2" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="83" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C7" t="s">
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D7" t="s">
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="95.25" customHeight="1">
+      <c r="B7" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="C9" t="s">
         <v>22</v>
       </c>
-      <c r="E7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="7">
+      <c r="D9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10">
         <v>1600000</v>
       </c>
-      <c r="D8" s="7">
-        <f>C8/About!$B$30</f>
+      <c r="D10">
+        <f>C10/About!$B$29</f>
         <v>120316.21738997873</v>
       </c>
-      <c r="E8" s="6">
-        <f>D8*About!$A$17</f>
+      <c r="E10" s="5">
+        <f>D10*About!$A$14</f>
         <v>116869.40496458152</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="7">
+      <c r="F10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="B11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="6">
+        <v>2797808</v>
+      </c>
+      <c r="D11" s="7">
+        <v>352813.11</v>
+      </c>
+      <c r="E11" s="5">
+        <f>D11*About!$A$14</f>
+        <v>342705.73929161596</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="B12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12">
         <v>13850000</v>
       </c>
-      <c r="D9" s="7">
-        <f>C9/About!$B$30</f>
+      <c r="D12">
+        <f>C12/About!$B$29</f>
         <v>1041487.2567820033</v>
       </c>
-      <c r="E9" s="8">
-        <f>D9*About!$A$17</f>
+      <c r="E12" s="5">
+        <f>D12*About!$A$14</f>
         <v>1011650.7867246587</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="C14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="B15" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="6">
+        <v>2000000</v>
+      </c>
+      <c r="D15" s="9">
+        <f>C15*About!A16</f>
+        <v>1694608.2592168872</v>
+      </c>
+      <c r="F15">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B7:F7"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="B4" r:id="rId2" xr:uid="{FA701A0E-3B13-2E4E-86C4-E7E4D696CC37}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -866,26 +924,197 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="16.5" customWidth="1"/>
+    <col min="1" max="2" width="16.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2">
       <c r="B1" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="9">
-        <f>Mexico!E9</f>
-        <v>1011650.7867246587</v>
+        <v>32</v>
+      </c>
+      <c r="B2" s="8">
+        <f>Mexico!D15</f>
+        <v>1694608.2592168872</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009A9DAB439B36DB4795F39C4E722C7BC4" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="44674c89fa9bc5e97a878a6680c46188">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="79748b23-d81a-423e-9112-21109dc864e6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="447839a363ea5a12024b5bf1ab53ed90" ns2:_="">
+    <xsd:import namespace="79748b23-d81a-423e-9112-21109dc864e6"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="79748b23-d81a-423e-9112-21109dc864e6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55E723E2-6DC7-4512-B42B-913F6DC408F1}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED8A4A89-CB37-46A1-B23B-360F77ABB45F}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DA52DC3-B7BC-4D08-8BBD-9D6D8AD2E73D}"/>
 </file>
--- a/InputData/add-outputs/VoaSL/Value of a Statistical Life.xlsx
+++ b/InputData/add-outputs/VoaSL/Value of a Statistical Life.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28318"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreazafra/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachel Goldstein\Desktop\EPS Models\Mexico EPS\InputData\add-outputs\VoaSL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{6E7A770A-7C28-0545-8D7C-1EB6139DDDB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C07C382-D83B-4BDF-89DC-90D091D010E7}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A83E6DD-4F75-48CB-A65F-FC37C57EBF1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="35080" yWindow="2640" windowWidth="27000" windowHeight="18160" firstSheet="2" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="44145" yWindow="1230" windowWidth="22785" windowHeight="14115" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -147,7 +147,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -214,11 +214,11 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
@@ -526,17 +526,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B37"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="38.28515625" customWidth="1"/>
+    <col min="2" max="2" width="38.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -544,75 +544,75 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>0.97135205460935392</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>0.84730412960844359</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>14</v>
       </c>
@@ -620,7 +620,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2006</v>
       </c>
@@ -628,7 +628,7 @@
         <v>10.901017260273969</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2007</v>
       </c>
@@ -636,7 +636,7 @@
         <v>10.926903013698627</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2008</v>
       </c>
@@ -644,7 +644,7 @@
         <v>11.138301912568313</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>2009</v>
       </c>
@@ -652,7 +652,7 @@
         <v>13.509501369863028</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>2010</v>
       </c>
@@ -660,7 +660,7 @@
         <v>12.636678082191793</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>2011</v>
       </c>
@@ -668,7 +668,7 @@
         <v>12.427292876712329</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>2012</v>
       </c>
@@ -676,7 +676,7 @@
         <v>13.168531967213106</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>2013</v>
       </c>
@@ -684,7 +684,7 @@
         <v>12.767464383561641</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>2014</v>
       </c>
@@ -692,7 +692,7 @@
         <v>13.298290410958895</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>2015</v>
       </c>
@@ -700,7 +700,7 @@
         <v>15.854175890410984</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>2016</v>
       </c>
@@ -708,7 +708,7 @@
         <v>18.656701092896164</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>2017</v>
       </c>
@@ -716,7 +716,7 @@
         <v>18.929111232876703</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>2018</v>
       </c>
@@ -724,7 +724,7 @@
         <v>18.822825165562914</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>2019</v>
       </c>
@@ -732,7 +732,7 @@
         <v>19.260525900000001</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>2020</v>
       </c>
@@ -740,7 +740,7 @@
         <v>21.493461509999999</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>2021</v>
       </c>
@@ -748,7 +748,7 @@
         <v>20.280012648221323</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>12</v>
       </c>
@@ -762,20 +762,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="43.28515625" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.33203125" customWidth="1"/>
+    <col min="3" max="3" width="13.109375" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -783,7 +783,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -791,7 +791,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -799,21 +799,21 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="95.25" customHeight="1">
-      <c r="B7" s="10" t="s">
+    <row r="7" spans="1:6" ht="95.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
         <v>22</v>
       </c>
@@ -827,7 +827,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>26</v>
       </c>
@@ -846,7 +846,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>27</v>
       </c>
@@ -864,7 +864,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>28</v>
       </c>
@@ -883,7 +883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C14" t="s">
         <v>29</v>
       </c>
@@ -891,14 +891,14 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>30</v>
       </c>
       <c r="C15" s="6">
         <v>2000000</v>
       </c>
-      <c r="D15" s="9">
+      <c r="D15" s="8">
         <f>C15*About!A16</f>
         <v>1694608.2592168872</v>
       </c>
@@ -924,21 +924,21 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="16.42578125" customWidth="1"/>
+    <col min="1" max="2" width="16.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B1" s="4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="10">
         <f>Mexico!D15</f>
         <v>1694608.2592168872</v>
       </c>
@@ -949,6 +949,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009A9DAB439B36DB4795F39C4E722C7BC4" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="44674c89fa9bc5e97a878a6680c46188">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="79748b23-d81a-423e-9112-21109dc864e6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="447839a363ea5a12024b5bf1ab53ed90" ns2:_="">
     <xsd:import namespace="79748b23-d81a-423e-9112-21109dc864e6"/>
@@ -1092,29 +1107,37 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DA52DC3-B7BC-4D08-8BBD-9D6D8AD2E73D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED8A4A89-CB37-46A1-B23B-360F77ABB45F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55E723E2-6DC7-4512-B42B-913F6DC408F1}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED8A4A89-CB37-46A1-B23B-360F77ABB45F}"/>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DA52DC3-B7BC-4D08-8BBD-9D6D8AD2E73D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55E723E2-6DC7-4512-B42B-913F6DC408F1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="79748b23-d81a-423e-9112-21109dc864e6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>